--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0003_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0003_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13836,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="CJ38" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK38" s="0">
         <v>0</v>
@@ -14024,7 +14023,7 @@
         <v>0</v>
       </c>
       <c r="AD39" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE39" s="0">
         <v>0</v>
@@ -14443,7 +14442,7 @@
         <v>0</v>
       </c>
       <c r="AW40" s="0">
-        <v>0.18837459634015053</v>
+        <v>0.18837459634015052</v>
       </c>
       <c r="AX40" s="0">
         <v>0</v>
@@ -14500,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="BP40" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ40" s="0">
         <v>0</v>
@@ -14784,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="AP41" s="0">
-        <v>2.5165562913907405</v>
+        <v>2.5165562913907404</v>
       </c>
       <c r="AQ41" s="0">
         <v>0</v>
@@ -15089,7 +15088,7 @@
         <v>0.13786764705882343</v>
       </c>
       <c r="W42" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X42" s="0">
         <v>13.246162592382024</v>
@@ -15750,7 +15749,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="0">
-        <v>0.17561465127947804</v>
+        <v>0.17561465127947803</v>
       </c>
       <c r="C44" s="0">
         <v>0.41537781705700366</v>
@@ -15852,7 +15851,7 @@
         <v>3.7397385223472144</v>
       </c>
       <c r="AJ44" s="0">
-        <v>8.0495356037151638</v>
+        <v>8.0495356037151637</v>
       </c>
       <c r="AK44" s="0">
         <v>10.809003788722968</v>
@@ -15867,7 +15866,7 @@
         <v>0</v>
       </c>
       <c r="AO44" s="0">
-        <v>3.1460674157303346</v>
+        <v>3.1460674157303345</v>
       </c>
       <c r="AP44" s="0">
         <v>13.686534216335529</v>
@@ -15885,7 +15884,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV44" s="0">
         <v>3.9123630672926417</v>
@@ -15933,7 +15932,7 @@
         <v>0.60807075732448812</v>
       </c>
       <c r="BK44" s="0">
-        <v>6.8823408201112653</v>
+        <v>6.8823408201112652</v>
       </c>
       <c r="BL44" s="0">
         <v>0.64959877722583048</v>
@@ -16047,7 +16046,7 @@
         <v>0</v>
       </c>
       <c r="CW44" s="0">
-        <v>1.3469239170003629</v>
+        <v>1.3469239170003628</v>
       </c>
       <c r="CX44" s="0">
         <v>0</v>
@@ -16109,7 +16108,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>0.18113754377490624</v>
+        <v>0.18113754377490623</v>
       </c>
       <c r="B45" s="0">
         <v>1.3923733065730044</v>
@@ -16172,7 +16171,7 @@
         <v>0.16731734523145553</v>
       </c>
       <c r="V45" s="0">
-        <v>4.2738970588235255</v>
+        <v>4.2738970588235254</v>
       </c>
       <c r="W45" s="0">
         <v>10.769230769230759</v>
@@ -16217,7 +16216,7 @@
         <v>3.6842105263157858</v>
       </c>
       <c r="AK45" s="0">
-        <v>5.8613773122353417</v>
+        <v>5.8613773122353416</v>
       </c>
       <c r="AL45" s="0">
         <v>0.2708454246469334</v>
@@ -16415,7 +16414,7 @@
         <v>0.19175455417066137</v>
       </c>
       <c r="CY45" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ45" s="0">
         <v>0.65252854812397987</v>
@@ -16451,7 +16450,7 @@
         <v>10.365853658536576</v>
       </c>
       <c r="DK45" s="0">
-        <v>8.1830790568654575</v>
+        <v>8.1830790568654574</v>
       </c>
       <c r="DL45" s="0">
         <v>1.3054830287206254</v>
@@ -16489,7 +16488,7 @@
         <v>6.7745545321511509</v>
       </c>
       <c r="G46" s="0">
-        <v>5.568910256410252</v>
+        <v>5.5689102564102519</v>
       </c>
       <c r="H46" s="0">
         <v>1.9679079624583695</v>
@@ -16531,7 +16530,7 @@
         <v>4.2204466297889738</v>
       </c>
       <c r="U46" s="0">
-        <v>0.94813162297824794</v>
+        <v>0.94813162297824793</v>
       </c>
       <c r="V46" s="0">
         <v>9.0533088235294041</v>
@@ -16777,7 +16776,7 @@
         <v>1.4860977948226257</v>
       </c>
       <c r="CY46" s="0">
-        <v>0.24313153415998035</v>
+        <v>0.24313153415998034</v>
       </c>
       <c r="CZ46" s="0">
         <v>2.4236774644604964</v>
@@ -16833,7 +16832,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.7532906653785903</v>
+        <v>2.7532906653785902</v>
       </c>
       <c r="B47" s="0">
         <v>10.336176618163622</v>
@@ -16887,7 +16886,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="0">
-        <v>0.40401225968236471</v>
+        <v>0.4040122596823647</v>
       </c>
       <c r="T47" s="0">
         <v>9.1989346445400972</v>
@@ -16971,7 +16970,7 @@
         <v>0.16694490818030128</v>
       </c>
       <c r="AU47" s="0">
-        <v>3.4124629080118854</v>
+        <v>3.4124629080118853</v>
       </c>
       <c r="AV47" s="0">
         <v>11.647663760339871</v>
@@ -16992,7 +16991,7 @@
         <v>14.344133375275312</v>
       </c>
       <c r="BB47" s="0">
-        <v>0.47309284447072964</v>
+        <v>0.47309284447072963</v>
       </c>
       <c r="BC47" s="0">
         <v>11.94768918232611</v>
@@ -17007,7 +17006,7 @@
         <v>7.1636817992503463</v>
       </c>
       <c r="BG47" s="0">
-        <v>7.9852125693161185</v>
+        <v>7.9852125693161184</v>
       </c>
       <c r="BH47" s="0">
         <v>0.87014725568942852</v>
@@ -17019,7 +17018,7 @@
         <v>0</v>
       </c>
       <c r="BK47" s="0">
-        <v>9.6023078508139737</v>
+        <v>9.6023078508139736</v>
       </c>
       <c r="BL47" s="0">
         <v>12.667176155903766</v>
@@ -17055,7 +17054,7 @@
         <v>10.810810810810862</v>
       </c>
       <c r="BW47" s="0">
-        <v>1.0526315789473733</v>
+        <v>1.0526315789473732</v>
       </c>
       <c r="BX47" s="0">
         <v>5.8897770298696113</v>
@@ -17115,7 +17114,7 @@
         <v>7.0512051804773082</v>
       </c>
       <c r="CQ47" s="0">
-        <v>8.7776332899870369</v>
+        <v>8.7776332899870368</v>
       </c>
       <c r="CR47" s="0">
         <v>8.0217321828060459</v>
@@ -17127,7 +17126,7 @@
         <v>13.416099319183083</v>
       </c>
       <c r="CU47" s="0">
-        <v>5.9880239520958361</v>
+        <v>5.988023952095836</v>
       </c>
       <c r="CV47" s="0">
         <v>2.0522388059701591</v>
@@ -17195,7 +17194,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>7.2575775872479103</v>
+        <v>7.2575775872479102</v>
       </c>
       <c r="B48" s="0">
         <v>14.124435524335162</v>
@@ -17222,7 +17221,7 @@
         <v>9.2857142857142776</v>
       </c>
       <c r="J48" s="0">
-        <v>3.6447343180510226</v>
+        <v>3.6447343180510225</v>
       </c>
       <c r="K48" s="0">
         <v>11.11744583808437</v>
@@ -17674,7 +17673,7 @@
         <v>0.46339202965708948</v>
       </c>
       <c r="AN49" s="0">
-        <v>4.4328552803129036</v>
+        <v>4.4328552803129035</v>
       </c>
       <c r="AO49" s="0">
         <v>4.4494382022471877</v>
@@ -17997,7 +17996,7 @@
         <v>6.8634179821551076</v>
       </c>
       <c r="AA50" s="0">
-        <v>17.238346525945453</v>
+        <v>17.238346525945452</v>
       </c>
       <c r="AB50" s="0">
         <v>0</v>
@@ -18168,7 +18167,7 @@
         <v>1.1428571428571419</v>
       </c>
       <c r="CF50" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG50" s="0">
         <v>0</v>
@@ -18548,7 +18547,7 @@
         <v>2.6649638143890995</v>
       </c>
       <c r="CL51" s="0">
-        <v>0.047366426676771462</v>
+        <v>0.047366426676771461</v>
       </c>
       <c r="CM51" s="0">
         <v>0</v>
@@ -18560,7 +18559,7 @@
         <v>0.63475271092303565</v>
       </c>
       <c r="CP51" s="0">
-        <v>7.4949034656433558</v>
+        <v>7.4949034656433557</v>
       </c>
       <c r="CQ51" s="0">
         <v>0.048764629388816601</v>
@@ -18697,7 +18696,7 @@
         <v>8.9531680440771275</v>
       </c>
       <c r="S52" s="0">
-        <v>13.889662858735012</v>
+        <v>13.889662858735011</v>
       </c>
       <c r="T52" s="0">
         <v>0.83999180495799963</v>
@@ -18721,7 +18720,7 @@
         <v>0.68634179821551078</v>
       </c>
       <c r="AA52" s="0">
-        <v>6.1565523306948054</v>
+        <v>6.1565523306948053</v>
       </c>
       <c r="AB52" s="0">
         <v>0</v>
@@ -18772,7 +18771,7 @@
         <v>2.9613733905579371</v>
       </c>
       <c r="AR52" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS52" s="0">
         <v>0</v>
@@ -18865,7 +18864,7 @@
         <v>0.63882063882063833</v>
       </c>
       <c r="BW52" s="0">
-        <v>7.5877192982456077</v>
+        <v>7.5877192982456076</v>
       </c>
       <c r="BX52" s="0">
         <v>0</v>
@@ -18919,7 +18918,7 @@
         <v>0.035893754486719283</v>
       </c>
       <c r="CO52" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP52" s="0">
         <v>2.2544669624655214</v>
@@ -18967,7 +18966,7 @@
         <v>0</v>
       </c>
       <c r="DE52" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF52" s="0">
         <v>0.15337423312883422</v>
@@ -19000,7 +18999,7 @@
         <v>2.4271844660194151</v>
       </c>
       <c r="DP52" s="0">
-        <v>7.3943661971830919</v>
+        <v>7.3943661971830918</v>
       </c>
     </row>
     <row r="53">
@@ -19020,7 +19019,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="0">
-        <v>0.068864594990100656</v>
+        <v>0.068864594990100655</v>
       </c>
       <c r="G53" s="0">
         <v>0.2403846153846152</v>
@@ -19209,7 +19208,7 @@
         <v>0</v>
       </c>
       <c r="BQ53" s="0">
-        <v>9.691313711414205</v>
+        <v>9.6913137114142049</v>
       </c>
       <c r="BR53" s="0">
         <v>0</v>
@@ -19221,7 +19220,7 @@
         <v>0</v>
       </c>
       <c r="BU53" s="0">
-        <v>16.599316133043193</v>
+        <v>16.599316133043192</v>
       </c>
       <c r="BV53" s="0">
         <v>0.14742014742014728</v>
@@ -19613,10 +19612,10 @@
         <v>0.61538461538461486</v>
       </c>
       <c r="CE54" s="0">
-        <v>18.857142857142844</v>
+        <v>18.857142857142843</v>
       </c>
       <c r="CF54" s="0">
-        <v>17.789291882556118</v>
+        <v>17.789291882556117</v>
       </c>
       <c r="CG54" s="0">
         <v>0</v>
@@ -19631,7 +19630,7 @@
         <v>0</v>
       </c>
       <c r="CK54" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL54" s="0">
         <v>0</v>
@@ -20035,7 +20034,7 @@
         <v>0.047938638542665342</v>
       </c>
       <c r="CY55" s="0">
-        <v>0.26744468757597834</v>
+        <v>0.26744468757597833</v>
       </c>
       <c r="CZ55" s="0">
         <v>0</v>
@@ -24211,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV67" s="0">
         <v>0</v>
@@ -25243,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="0">
-        <v>6.6666666666666608</v>
+        <v>6.6666666666666607</v>
       </c>
       <c r="AD70" s="0">
         <v>0</v>
@@ -25270,7 +25269,7 @@
         <v>0</v>
       </c>
       <c r="AL70" s="0">
-        <v>7.0613271425807636</v>
+        <v>7.0613271425807635</v>
       </c>
       <c r="AM70" s="0">
         <v>0</v>
@@ -25309,7 +25308,7 @@
         <v>0</v>
       </c>
       <c r="AY70" s="0">
-        <v>0.3640040444893829</v>
+        <v>0.36400404448938289</v>
       </c>
       <c r="AZ70" s="0">
         <v>0.3519822156354202</v>
@@ -25360,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="BP70" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ70" s="0">
         <v>11.127063890882976</v>
@@ -26087,7 +26086,7 @@
         <v>0.72751322751322678</v>
       </c>
       <c r="BQ72" s="0">
-        <v>8.2196697774587158</v>
+        <v>8.2196697774587157</v>
       </c>
       <c r="BR72" s="0">
         <v>0.96875756841850236</v>
@@ -26105,7 +26104,7 @@
         <v>0.049140049140049095</v>
       </c>
       <c r="BW72" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX72" s="0">
         <v>0</v>
@@ -26159,7 +26158,7 @@
         <v>0</v>
       </c>
       <c r="CO72" s="0">
-        <v>5.9508066649034595</v>
+        <v>5.9508066649034594</v>
       </c>
       <c r="CP72" s="0">
         <v>0</v>
@@ -26344,7 +26343,7 @@
         <v>0</v>
       </c>
       <c r="AH73" s="0">
-        <v>8.6822074215033212</v>
+        <v>8.6822074215033211</v>
       </c>
       <c r="AI73" s="0">
         <v>0</v>
@@ -26356,7 +26355,7 @@
         <v>0</v>
       </c>
       <c r="AL73" s="0">
-        <v>8.8024763010253349</v>
+        <v>8.8024763010253348</v>
       </c>
       <c r="AM73" s="0">
         <v>0</v>
@@ -26697,7 +26696,7 @@
         <v>0</v>
       </c>
       <c r="AE74" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF74" s="0">
         <v>0</v>
@@ -26892,7 +26891,7 @@
         <v>3.6410923276983063</v>
       </c>
       <c r="CR74" s="0">
-        <v>4.8098434004474227</v>
+        <v>4.8098434004474226</v>
       </c>
       <c r="CS74" s="0">
         <v>3.8478549314462596</v>
@@ -27032,7 +27031,7 @@
         <v>2.063580591187951</v>
       </c>
       <c r="V75" s="0">
-        <v>6.0202205882352891</v>
+        <v>6.020220588235289</v>
       </c>
       <c r="W75" s="0">
         <v>2.3076923076923057</v>
@@ -27340,7 +27339,7 @@
         <v>7.1674768007070195</v>
       </c>
       <c r="D76" s="0">
-        <v>5.5651176133103793</v>
+        <v>5.5651176133103792</v>
       </c>
       <c r="E76" s="0">
         <v>11.512942715634043</v>
@@ -27637,7 +27636,7 @@
         <v>0.047938638542665342</v>
       </c>
       <c r="CY76" s="0">
-        <v>0.26744468757597834</v>
+        <v>0.26744468757597833</v>
       </c>
       <c r="CZ76" s="0">
         <v>2.4469820554649244</v>
@@ -27729,7 +27728,7 @@
         <v>2.3441662226957893</v>
       </c>
       <c r="M77" s="0">
-        <v>3.4095634095634067</v>
+        <v>3.4095634095634066</v>
       </c>
       <c r="N77" s="0">
         <v>11.401869158878494</v>
@@ -27816,7 +27815,7 @@
         <v>9.6629213483145993</v>
       </c>
       <c r="AP77" s="0">
-        <v>2.2958057395143468</v>
+        <v>2.2958057395143467</v>
       </c>
       <c r="AQ77" s="0">
         <v>3.090128755364804</v>
@@ -27840,16 +27839,16 @@
         <v>10.495156081808387</v>
       </c>
       <c r="AX77" s="0">
-        <v>2.856274688544513</v>
+        <v>2.8562746885445129</v>
       </c>
       <c r="AY77" s="0">
         <v>1.4155712841253778</v>
       </c>
       <c r="AZ77" s="0">
-        <v>1.9266394961096685</v>
+        <v>1.9266394961096684</v>
       </c>
       <c r="BA77" s="0">
-        <v>9.5942120163573375</v>
+        <v>9.5942120163573374</v>
       </c>
       <c r="BB77" s="0">
         <v>9.7575399172087423</v>
@@ -27861,7 +27860,7 @@
         <v>6.680369989722502</v>
       </c>
       <c r="BE77" s="0">
-        <v>6.0947022972339378</v>
+        <v>6.0947022972339377</v>
       </c>
       <c r="BF77" s="0">
         <v>0.62473969179508482</v>
@@ -27876,7 +27875,7 @@
         <v>0</v>
       </c>
       <c r="BJ77" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK77" s="0">
         <v>9.1695858232021354</v>
@@ -28070,7 +28069,7 @@
         <v>2.5511634426689072</v>
       </c>
       <c r="F78" s="0">
-        <v>0.69725402427476913</v>
+        <v>0.69725402427476912</v>
       </c>
       <c r="G78" s="0">
         <v>1.4022435897435885</v>
@@ -28127,7 +28126,7 @@
         <v>0</v>
       </c>
       <c r="Y78" s="0">
-        <v>7.6257861635220055</v>
+        <v>7.6257861635220054</v>
       </c>
       <c r="Z78" s="0">
         <v>11.461908030199028</v>
@@ -28220,7 +28219,7 @@
         <v>0.21584560690705923</v>
       </c>
       <c r="BD78" s="0">
-        <v>2.466598150051385</v>
+        <v>2.4665981500513849</v>
       </c>
       <c r="BE78" s="0">
         <v>3.0004688232536307</v>
@@ -28229,7 +28228,7 @@
         <v>2.6655560183256952</v>
       </c>
       <c r="BG78" s="0">
-        <v>2.2181146025877983</v>
+        <v>2.2181146025877982</v>
       </c>
       <c r="BH78" s="0">
         <v>5.15394912985274</v>
@@ -28298,7 +28297,7 @@
         <v>0</v>
       </c>
       <c r="CD78" s="0">
-        <v>3.3461538461538432</v>
+        <v>3.3461538461538431</v>
       </c>
       <c r="CE78" s="0">
         <v>4.1904761904761862</v>
@@ -28316,7 +28315,7 @@
         <v>7.6206322795341022</v>
       </c>
       <c r="CJ78" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK78" s="0">
         <v>5.014899957428689</v>
@@ -28417,7 +28416,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.7751479289940813</v>
+        <v>1.7751479289940812</v>
       </c>
       <c r="B79" s="0">
         <v>0.050175614651279433</v>
@@ -28444,7 +28443,7 @@
         <v>0.3820598006644515</v>
       </c>
       <c r="J79" s="0">
-        <v>6.5605217724918426</v>
+        <v>6.5605217724918425</v>
       </c>
       <c r="K79" s="0">
         <v>0.11402508551881405</v>
@@ -28588,7 +28587,7 @@
         <v>0.75011720581340768</v>
       </c>
       <c r="BF79" s="0">
-        <v>6.4139941690962044</v>
+        <v>6.4139941690962043</v>
       </c>
       <c r="BG79" s="0">
         <v>5.2865064695009192</v>
@@ -28693,7 +28692,7 @@
         <v>2.0100502512562795</v>
       </c>
       <c r="CO79" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP79" s="0">
         <v>8.3103489627053531</v>
@@ -28741,7 +28740,7 @@
         <v>0</v>
       </c>
       <c r="DE79" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF79" s="0">
         <v>0</v>
@@ -28920,7 +28919,7 @@
         <v>0</v>
       </c>
       <c r="AV80" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW80" s="0">
         <v>4.6017222820236769</v>
@@ -29052,7 +29051,7 @@
         <v>9.5025153717160347</v>
       </c>
       <c r="CN80" s="0">
-        <v>5.5994256999282071</v>
+        <v>5.599425699928207</v>
       </c>
       <c r="CO80" s="0">
         <v>0</v>
@@ -29222,7 +29221,7 @@
         <v>9.1468777484608541</v>
       </c>
       <c r="AB81" s="0">
-        <v>1.1036174126302874</v>
+        <v>1.1036174126302873</v>
       </c>
       <c r="AC81" s="0">
         <v>0</v>
@@ -29399,7 +29398,7 @@
         <v>0.46376043460977834</v>
       </c>
       <c r="CI81" s="0">
-        <v>0.26622296173044902</v>
+        <v>0.26622296173044901</v>
       </c>
       <c r="CJ81" s="0">
         <v>1.3598987982289679</v>
@@ -29578,7 +29577,7 @@
         <v>1.4150943396226561</v>
       </c>
       <c r="Z82" s="0">
-        <v>0.34317089910775917</v>
+        <v>0.34317089910775916</v>
       </c>
       <c r="AA82" s="0">
         <v>7.2999120492524936</v>
@@ -29617,7 +29616,7 @@
         <v>0</v>
       </c>
       <c r="AM82" s="0">
-        <v>6.765523632993582</v>
+        <v>6.7655236329935819</v>
       </c>
       <c r="AN82" s="0">
         <v>1.0430247718383419</v>
@@ -29698,7 +29697,7 @@
         <v>3.9979141317573852</v>
       </c>
       <c r="BN82" s="0">
-        <v>0.031046258925799757</v>
+        <v>0.031046258925799756</v>
       </c>
       <c r="BO82" s="0">
         <v>0.37149611617697104</v>
@@ -29857,7 +29856,7 @@
         <v>1.562500000000016</v>
       </c>
       <c r="DO82" s="0">
-        <v>4.1262135922330519</v>
+        <v>4.1262135922330518</v>
       </c>
       <c r="DP82" s="0">
         <v>0</v>
@@ -29934,7 +29933,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="0">
-        <v>8.243320068220573</v>
+        <v>8.2433200682205729</v>
       </c>
       <c r="Y83" s="0">
         <v>0.31446540880503121</v>
@@ -30718,7 +30717,7 @@
         <v>0</v>
       </c>
       <c r="AR85" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS85" s="0">
         <v>0.99206349206349109</v>
@@ -30769,7 +30768,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="0">
-        <v>6.6379774072081697</v>
+        <v>6.6379774072081696</v>
       </c>
       <c r="BJ85" s="0">
         <v>4.4665561083471497</v>
@@ -31212,7 +31211,7 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="0">
-        <v>4.2061986084756447</v>
+        <v>4.2061986084756446</v>
       </c>
       <c r="CK86" s="0">
         <v>0</v>
@@ -31284,7 +31283,7 @@
         <v>4.5731707317073127</v>
       </c>
       <c r="DH86" s="0">
-        <v>1.8716577540106934</v>
+        <v>1.8716577540106933</v>
       </c>
       <c r="DI86" s="0">
         <v>0</v>
@@ -31780,7 +31779,7 @@
         <v>0.03040437823046516</v>
       </c>
       <c r="AJ88" s="0">
-        <v>1.238390092879256</v>
+        <v>1.2383900928792559</v>
       </c>
       <c r="AK88" s="0">
         <v>0</v>
@@ -32124,7 +32123,7 @@
         <v>0</v>
       </c>
       <c r="AD89" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE89" s="0">
         <v>0</v>
@@ -32298,7 +32297,7 @@
         <v>0</v>
       </c>
       <c r="CJ89" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK89" s="0">
         <v>0</v>
@@ -32358,7 +32357,7 @@
         <v>0</v>
       </c>
       <c r="DD89" s="0">
-        <v>10.801457194899808</v>
+        <v>10.801457194899807</v>
       </c>
       <c r="DE89" s="0">
         <v>0</v>
@@ -32624,7 +32623,7 @@
         <v>0</v>
       </c>
       <c r="BX90" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY90" s="0">
         <v>0</v>
@@ -32639,7 +32638,7 @@
         <v>0</v>
       </c>
       <c r="CC90" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD90" s="0">
         <v>0</v>
@@ -33109,7 +33108,7 @@
         <v>0</v>
       </c>
       <c r="DM91" s="0">
-        <v>6.1965811965811915</v>
+        <v>6.1965811965811914</v>
       </c>
       <c r="DN91" s="0">
         <v>0</v>
@@ -34865,7 +34864,7 @@
         <v>0</v>
       </c>
       <c r="CU96" s="0">
-        <v>4.491017964071852</v>
+        <v>4.4910179640718519</v>
       </c>
       <c r="CV96" s="0">
         <v>0</v>
